--- a/SGC-CKN/Excel/48953b5b-b392-4726-b9ae-e7c9a983e183_Thi_công_cọc_khoan_nhồi_P1-163_D800_06-04-2026.xlsx
+++ b/SGC-CKN/Excel/48953b5b-b392-4726-b9ae-e7c9a983e183_Thi_công_cọc_khoan_nhồi_P1-163_D800_06-04-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="61">
   <si>
     <t>Dự án</t>
   </si>
@@ -109,7 +109,7 @@
     <t>2</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">07:40
@@ -119,7 +119,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>Cát pha xám ghi, xám nâu TT dẻo</t>
+    <t>Cát pha, xám ghi, xám nâu, xám vàng, TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">08:00
@@ -139,7 +139,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
+    <t>Sét xám vàng, nâu vàng, xám xanh, TT nửa cứng</t>
   </si>
   <si>
     <t xml:space="preserve">10:00
@@ -149,23 +149,19 @@
     <t>6</t>
   </si>
   <si>
-    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10:50
-06/04/2026</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
     <t xml:space="preserve">10:30
 06/04/2026</t>
   </si>
   <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>Cát thô, xám vàng, xám xanh, xám nâu, KC chặt</t>
+  </si>
+  <si>
     <t xml:space="preserve">13:50
 06/04/2026</t>
   </si>
@@ -173,7 +169,7 @@
     <t>8</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">16:15
@@ -356,12 +352,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
+        <fgColor rgb="FFFED7AA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFED7AA"/>
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -533,17 +529,17 @@
     <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1149,16 +1145,16 @@
         <v>-0.61</v>
       </c>
       <c r="G11" s="5">
-        <v>-2.11</v>
+        <v>-1.5</v>
       </c>
       <c r="H11" s="5">
         <v>0.17</v>
       </c>
       <c r="I11" s="5">
-        <v>1.5</v>
+        <v>0.89</v>
       </c>
       <c r="J11" s="8">
-        <v>9</v>
+        <v>5.34</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>29</v>
@@ -1181,19 +1177,19 @@
         <v>32</v>
       </c>
       <c r="F12" s="9">
-        <v>-2.11</v>
+        <v>-1.5</v>
       </c>
       <c r="G12" s="9">
-        <v>-10.11</v>
+        <v>-4.5</v>
       </c>
       <c r="H12" s="9">
         <v>0.25</v>
       </c>
       <c r="I12" s="9">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J12" s="8">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>29</v>
@@ -1216,19 +1212,19 @@
         <v>35</v>
       </c>
       <c r="F13" s="12">
-        <v>-10.11</v>
+        <v>-4.5</v>
       </c>
       <c r="G13" s="12">
-        <v>-17.91</v>
+        <v>-7.8</v>
       </c>
       <c r="H13" s="12">
         <v>0.33</v>
       </c>
       <c r="I13" s="12">
-        <v>7.8</v>
+        <v>3.3</v>
       </c>
       <c r="J13" s="8">
-        <v>23.4</v>
+        <v>9.9</v>
       </c>
       <c r="K13" s="13" t="s">
         <v>29</v>
@@ -1251,19 +1247,19 @@
         <v>38</v>
       </c>
       <c r="F14" s="15">
-        <v>-17.91</v>
+        <v>-7.8</v>
       </c>
       <c r="G14" s="15">
-        <v>-26.41</v>
+        <v>-16.5</v>
       </c>
       <c r="H14" s="15">
         <v>1.5</v>
       </c>
       <c r="I14" s="15">
-        <v>8.5</v>
+        <v>8.7</v>
       </c>
       <c r="J14" s="8">
-        <v>5.67</v>
+        <v>5.8</v>
       </c>
       <c r="K14" s="16" t="s">
         <v>29</v>
@@ -1286,19 +1282,19 @@
         <v>41</v>
       </c>
       <c r="F15" s="18">
-        <v>-26.41</v>
+        <v>-16.5</v>
       </c>
       <c r="G15" s="18">
-        <v>-34.71</v>
+        <v>-21.8</v>
       </c>
       <c r="H15" s="18">
         <v>0.5</v>
       </c>
       <c r="I15" s="18">
-        <v>8.3</v>
+        <v>5.3</v>
       </c>
       <c r="J15" s="8">
-        <v>16.6</v>
+        <v>10.6</v>
       </c>
       <c r="K15" s="19" t="s">
         <v>29</v>
@@ -1321,89 +1317,89 @@
         <v>44</v>
       </c>
       <c r="F16" s="21">
-        <v>-34.71</v>
+        <v>-21.8</v>
       </c>
       <c r="G16" s="21">
-        <v>-35.71</v>
+        <v>-25.8</v>
       </c>
       <c r="H16" s="21">
-        <v>0.83</v>
+        <v>0.5</v>
       </c>
       <c r="I16" s="21">
-        <v>1</v>
-      </c>
-      <c r="J16" s="24">
-        <v>1.2</v>
+        <v>4</v>
+      </c>
+      <c r="J16" s="8">
+        <v>8</v>
       </c>
       <c r="K16" s="22" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="26" t="s">
+      <c r="C17" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="D17" s="27" t="s">
+      <c r="D17" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="E17" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="F17" s="25">
-        <v>-35.71</v>
-      </c>
-      <c r="G17" s="25">
-        <v>-48.91</v>
-      </c>
-      <c r="H17" s="25">
+      <c r="F17" s="24">
+        <v>-25.8</v>
+      </c>
+      <c r="G17" s="24">
+        <v>-39</v>
+      </c>
+      <c r="H17" s="24">
         <v>3.33</v>
       </c>
-      <c r="I17" s="25">
+      <c r="I17" s="24">
         <v>13.2</v>
       </c>
-      <c r="J17" s="24">
+      <c r="J17" s="27">
         <v>3.96</v>
       </c>
-      <c r="K17" s="26" t="s">
+      <c r="K17" s="25" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B18" s="28" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="E18" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="D18" s="30" t="s">
-        <v>48</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>51</v>
-      </c>
       <c r="F18" s="28">
-        <v>-48.91</v>
+        <v>-39</v>
       </c>
       <c r="G18" s="28">
-        <v>-103.7</v>
+        <v>-43.89</v>
       </c>
       <c r="H18" s="28">
         <v>2.42</v>
       </c>
       <c r="I18" s="28">
-        <v>54.79</v>
-      </c>
-      <c r="J18" s="8">
-        <v>22.67</v>
+        <v>4.89</v>
+      </c>
+      <c r="J18" s="27">
+        <v>2.02</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>29</v>
@@ -1411,7 +1407,7 @@
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="31" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B21" s="31"/>
       <c r="C21" s="31"/>
@@ -1517,31 +1513,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1561,16 +1557,16 @@
         <v>-0.61</v>
       </c>
       <c r="F2" s="5">
-        <v>-2.11</v>
+        <v>-1.5</v>
       </c>
       <c r="G2" s="5">
         <v>0.17</v>
       </c>
       <c r="H2" s="5">
-        <v>1.5</v>
+        <v>0.89</v>
       </c>
       <c r="I2" s="8">
-        <v>9</v>
+        <v>5.34</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1587,19 +1583,19 @@
         <v>1</v>
       </c>
       <c r="E3" s="9">
-        <v>-2.11</v>
+        <v>-1.5</v>
       </c>
       <c r="F3" s="9">
-        <v>-10.11</v>
+        <v>-4.5</v>
       </c>
       <c r="G3" s="9">
         <v>0.25</v>
       </c>
       <c r="H3" s="9">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I3" s="8">
-        <v>32</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1616,19 +1612,19 @@
         <v>1</v>
       </c>
       <c r="E4" s="12">
-        <v>-10.11</v>
+        <v>-4.5</v>
       </c>
       <c r="F4" s="12">
-        <v>-17.91</v>
+        <v>-7.8</v>
       </c>
       <c r="G4" s="12">
         <v>0.33</v>
       </c>
       <c r="H4" s="12">
-        <v>7.8</v>
+        <v>3.3</v>
       </c>
       <c r="I4" s="8">
-        <v>23.4</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1645,19 +1641,19 @@
         <v>1</v>
       </c>
       <c r="E5" s="15">
-        <v>-17.91</v>
+        <v>-7.8</v>
       </c>
       <c r="F5" s="15">
-        <v>-26.41</v>
+        <v>-16.5</v>
       </c>
       <c r="G5" s="15">
         <v>1.5</v>
       </c>
       <c r="H5" s="15">
-        <v>8.5</v>
+        <v>8.7</v>
       </c>
       <c r="I5" s="8">
-        <v>5.67</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1674,19 +1670,19 @@
         <v>1</v>
       </c>
       <c r="E6" s="18">
-        <v>-26.41</v>
+        <v>-16.5</v>
       </c>
       <c r="F6" s="18">
-        <v>-34.71</v>
+        <v>-21.8</v>
       </c>
       <c r="G6" s="18">
         <v>0.5</v>
       </c>
       <c r="H6" s="18">
-        <v>8.3</v>
+        <v>5.3</v>
       </c>
       <c r="I6" s="8">
-        <v>16.6</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1703,47 +1699,47 @@
         <v>1</v>
       </c>
       <c r="E7" s="21">
-        <v>-34.71</v>
+        <v>-21.8</v>
       </c>
       <c r="F7" s="21">
-        <v>-35.71</v>
+        <v>-25.8</v>
       </c>
       <c r="G7" s="21">
-        <v>0.83</v>
+        <v>0.5</v>
       </c>
       <c r="H7" s="21">
+        <v>4</v>
+      </c>
+      <c r="I7" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="24">
+        <v>7</v>
+      </c>
+      <c r="B8" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" s="24">
         <v>1</v>
       </c>
-      <c r="I7" s="24">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="25">
-        <v>7</v>
-      </c>
-      <c r="B8" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="D8" s="25">
-        <v>1</v>
-      </c>
-      <c r="E8" s="25">
-        <v>-35.71</v>
-      </c>
-      <c r="F8" s="25">
-        <v>-48.91</v>
-      </c>
-      <c r="G8" s="25">
+      <c r="E8" s="24">
+        <v>-25.8</v>
+      </c>
+      <c r="F8" s="24">
+        <v>-39</v>
+      </c>
+      <c r="G8" s="24">
         <v>3.33</v>
       </c>
-      <c r="H8" s="25">
+      <c r="H8" s="24">
         <v>13.2</v>
       </c>
-      <c r="I8" s="24">
+      <c r="I8" s="27">
         <v>3.96</v>
       </c>
     </row>
@@ -1755,30 +1751,30 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
       </c>
       <c r="E9" s="28">
-        <v>-48.91</v>
+        <v>-39</v>
       </c>
       <c r="F9" s="28">
-        <v>-103.7</v>
+        <v>-43.89</v>
       </c>
       <c r="G9" s="28">
         <v>2.42</v>
       </c>
       <c r="H9" s="28">
-        <v>54.79</v>
-      </c>
-      <c r="I9" s="8">
-        <v>22.67</v>
+        <v>4.89</v>
+      </c>
+      <c r="I9" s="27">
+        <v>2.02</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B10" s="33" t="s">
         <v>29</v>
@@ -1793,16 +1789,16 @@
         <v>-0.61</v>
       </c>
       <c r="F10" s="33">
-        <v>-103.7</v>
+        <v>-43.89</v>
       </c>
       <c r="G10" s="33">
-        <v>9.33</v>
+        <v>9</v>
       </c>
       <c r="H10" s="33">
-        <v>103.09</v>
+        <v>43.28</v>
       </c>
       <c r="I10" s="33">
-        <v>11.05</v>
+        <v>4.81</v>
       </c>
     </row>
   </sheetData>
